--- a/samples/scenario_template.xlsx
+++ b/samples/scenario_template.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Results" sheetId="1" r:id="R26ddf87f715d466a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly path" sheetId="2" r:id="Rb39d9dc446154e72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly path by month" sheetId="3" r:id="Rd9a211061a304ad3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correlation" sheetId="4" r:id="Rb5a8673432b44c1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outside-use effects" sheetId="5" r:id="R2ac3cc7a030b44fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario" sheetId="6" r:id="R2533647ad666427c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uses not modelled" sheetId="7" r:id="R2837dce5b5f94b15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="8" r:id="R7f3c502fbfbb44b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="9" r:id="R64c139a5b7464b77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Results" sheetId="1" r:id="Rcbdacbb00b654949"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly path" sheetId="2" r:id="R435306591c374e82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly path by month" sheetId="3" r:id="R761f98ac371d46a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correlation" sheetId="4" r:id="R8a0e59a818764045"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outside-use effects" sheetId="5" r:id="R11e2cc77dd4f4d01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario" sheetId="6" r:id="R993cd5fa89ee4ae7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uses not modelled" sheetId="7" r:id="R48e180fa99ba4606"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="8" r:id="Rb43578d5d19c4835"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="9" r:id="R551f416980c74cb9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -427,6 +427,347 @@
 </x:styleSheet>
 </file>
 
+<file path=xl/drawings/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr sz="900">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>Simulated month-end cash: p10, median, p90 and zero</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>10th percentile month-end cash (USD, displayed in millions)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="A4B7D3"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Monthly path by month'!$B$2:$B$13</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Monthly path by month'!$F$2:$F$13</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,);"-"</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Median month-end cash (USD, displayed in millions)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="3987E5"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Monthly path by month'!$B$2:$B$13</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Monthly path by month'!$H$2:$H$13</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,);"-"</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>90th percentile month-end cash (USD, displayed in millions)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="A4B7D3"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Monthly path by month'!$B$2:$B$13</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Monthly path by month'!$I$2:$I$13</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,);"-"</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Zero reference (USD, displayed in millions)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="777777"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Monthly path by month'!$B$2:$B$13</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Monthly path by month'!$J$2:$J$13</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,);"-"</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:smooth val="0"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="750">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:r>
+                  <a:t>USD millions</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="#,##0,,;(#,##0,,)" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="750">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="750">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5cb5e369f06045f2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
@@ -1007,6 +1348,9 @@
     <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="54" customHeight="1">
@@ -1028,8 +1372,17 @@
       <x:c r="F1" s="32" t="str">
         <x:v>10th percentile month-end cash (USD, displayed in millions)</x:v>
       </x:c>
-      <x:c r="G1" s="33" t="str">
+      <x:c r="G1" s="32" t="str">
         <x:v>Share of trials below zero at this month end</x:v>
+      </x:c>
+      <x:c r="H1" s="32" t="str">
+        <x:v>Median month-end cash (USD, displayed in millions)</x:v>
+      </x:c>
+      <x:c r="I1" s="32" t="str">
+        <x:v>90th percentile month-end cash (USD, displayed in millions)</x:v>
+      </x:c>
+      <x:c r="J1" s="33" t="str">
+        <x:v>Zero reference (USD, displayed in millions)</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
@@ -1051,7 +1404,16 @@
       <x:c r="F2" s="13" t="n">
         <x:v>32111700903.862396</x:v>
       </x:c>
-      <x:c r="G2" s="34" t="n">
+      <x:c r="G2" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H2" s="13" t="n">
+        <x:v>32543640934.422478</x:v>
+      </x:c>
+      <x:c r="I2" s="13" t="n">
+        <x:v>33032113944.756496</x:v>
+      </x:c>
+      <x:c r="J2" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1074,7 +1436,16 @@
       <x:c r="F3" s="13" t="n">
         <x:v>28335275264.34795</x:v>
       </x:c>
-      <x:c r="G3" s="34" t="n">
+      <x:c r="G3" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H3" s="13" t="n">
+        <x:v>29194281396.461823</x:v>
+      </x:c>
+      <x:c r="I3" s="13" t="n">
+        <x:v>30176725709.829395</x:v>
+      </x:c>
+      <x:c r="J3" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1097,7 +1468,16 @@
       <x:c r="F4" s="13" t="n">
         <x:v>24557411043.891598</x:v>
       </x:c>
-      <x:c r="G4" s="34" t="n">
+      <x:c r="G4" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H4" s="13" t="n">
+        <x:v>25843599256.2782</x:v>
+      </x:c>
+      <x:c r="I4" s="13" t="n">
+        <x:v>27321651450.597527</x:v>
+      </x:c>
+      <x:c r="J4" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1120,7 +1500,16 @@
       <x:c r="F5" s="13" t="n">
         <x:v>20638339615.53734</x:v>
       </x:c>
-      <x:c r="G5" s="34" t="n">
+      <x:c r="G5" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="13" t="n">
+        <x:v>22353902413.675194</x:v>
+      </x:c>
+      <x:c r="I5" s="13" t="n">
+        <x:v>24321111825.127766</x:v>
+      </x:c>
+      <x:c r="J5" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1143,7 +1532,16 @@
       <x:c r="F6" s="13" t="n">
         <x:v>16857685631.685734</x:v>
       </x:c>
-      <x:c r="G6" s="34" t="n">
+      <x:c r="G6" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="13" t="n">
+        <x:v>19004611346.822044</x:v>
+      </x:c>
+      <x:c r="I6" s="13" t="n">
+        <x:v>21462810064.017548</x:v>
+      </x:c>
+      <x:c r="J6" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1166,7 +1564,16 @@
       <x:c r="F7" s="13" t="n">
         <x:v>13080761856.38868</x:v>
       </x:c>
-      <x:c r="G7" s="34" t="n">
+      <x:c r="G7" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="13" t="n">
+        <x:v>15656523133.862455</x:v>
+      </x:c>
+      <x:c r="I7" s="13" t="n">
+        <x:v>18605572385.110096</x:v>
+      </x:c>
+      <x:c r="J7" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1189,7 +1596,16 @@
       <x:c r="F8" s="13" t="n">
         <x:v>9159300914.392431</x:v>
       </x:c>
-      <x:c r="G8" s="34" t="n">
+      <x:c r="G8" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="13" t="n">
+        <x:v>12167852104.10709</x:v>
+      </x:c>
+      <x:c r="I8" s="13" t="n">
+        <x:v>15607989848.146132</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1212,7 +1628,16 @@
       <x:c r="F9" s="13" t="n">
         <x:v>3130748521.031528</x:v>
       </x:c>
-      <x:c r="G9" s="34" t="n">
+      <x:c r="G9" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="13" t="n">
+        <x:v>6566680026.082891</x:v>
+      </x:c>
+      <x:c r="I9" s="13" t="n">
+        <x:v>10500840470.741013</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1235,8 +1660,17 @@
       <x:c r="F10" s="13" t="n">
         <x:v>-648782871.5330231</x:v>
       </x:c>
-      <x:c r="G10" s="34" t="n">
+      <x:c r="G10" s="15" t="n">
         <x:v>0.1482</x:v>
+      </x:c>
+      <x:c r="H10" s="13" t="n">
+        <x:v>3218317866.4553847</x:v>
+      </x:c>
+      <x:c r="I10" s="13" t="n">
+        <x:v>7641252295.103267</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
@@ -1258,8 +1692,17 @@
       <x:c r="F11" s="13" t="n">
         <x:v>-4567786615.909948</x:v>
       </x:c>
-      <x:c r="G11" s="34" t="n">
+      <x:c r="G11" s="15" t="n">
         <x:v>0.528</x:v>
+      </x:c>
+      <x:c r="H11" s="13" t="n">
+        <x:v>-270777201.481009</x:v>
+      </x:c>
+      <x:c r="I11" s="13" t="n">
+        <x:v>4642180016.194417</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="32" customHeight="1">
@@ -1281,8 +1724,17 @@
       <x:c r="F12" s="13" t="n">
         <x:v>-8346310568.804653</x:v>
       </x:c>
-      <x:c r="G12" s="34" t="n">
+      <x:c r="G12" s="15" t="n">
         <x:v>0.8086</x:v>
+      </x:c>
+      <x:c r="H12" s="13" t="n">
+        <x:v>-3621015061.931224</x:v>
+      </x:c>
+      <x:c r="I12" s="13" t="n">
+        <x:v>1783172385.53767</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
@@ -1304,8 +1756,17 @@
       <x:c r="F13" s="13" t="n">
         <x:v>-16628558782.736282</x:v>
       </x:c>
-      <x:c r="G13" s="34" t="n">
+      <x:c r="G13" s="15" t="n">
         <x:v>0.9948</x:v>
+      </x:c>
+      <x:c r="H13" s="13" t="n">
+        <x:v>-11474076193.260612</x:v>
+      </x:c>
+      <x:c r="I13" s="13" t="n">
+        <x:v>-5579835245.119084</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="40" customHeight="1">
@@ -1327,7 +1788,16 @@
       <x:c r="F14" s="13" t="n">
         <x:v>32111700903.862396</x:v>
       </x:c>
-      <x:c r="G14" s="34" t="n">
+      <x:c r="G14" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" s="13" t="n">
+        <x:v>32543640934.422478</x:v>
+      </x:c>
+      <x:c r="I14" s="13" t="n">
+        <x:v>33032113944.756496</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1350,7 +1820,16 @@
       <x:c r="F15" s="13" t="n">
         <x:v>28335275264.34795</x:v>
       </x:c>
-      <x:c r="G15" s="34" t="n">
+      <x:c r="G15" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="13" t="n">
+        <x:v>29194281396.461823</x:v>
+      </x:c>
+      <x:c r="I15" s="13" t="n">
+        <x:v>30176725709.829395</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1373,7 +1852,16 @@
       <x:c r="F16" s="13" t="n">
         <x:v>24557411043.891598</x:v>
       </x:c>
-      <x:c r="G16" s="34" t="n">
+      <x:c r="G16" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="13" t="n">
+        <x:v>25843599256.2782</x:v>
+      </x:c>
+      <x:c r="I16" s="13" t="n">
+        <x:v>27321651450.597527</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1396,7 +1884,16 @@
       <x:c r="F17" s="13" t="n">
         <x:v>20638339615.53734</x:v>
       </x:c>
-      <x:c r="G17" s="34" t="n">
+      <x:c r="G17" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="13" t="n">
+        <x:v>22353902413.675194</x:v>
+      </x:c>
+      <x:c r="I17" s="13" t="n">
+        <x:v>24321111825.127766</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1419,7 +1916,16 @@
       <x:c r="F18" s="13" t="n">
         <x:v>16857685631.685734</x:v>
       </x:c>
-      <x:c r="G18" s="34" t="n">
+      <x:c r="G18" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="13" t="n">
+        <x:v>19004611346.822044</x:v>
+      </x:c>
+      <x:c r="I18" s="13" t="n">
+        <x:v>21462810064.017548</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1442,7 +1948,16 @@
       <x:c r="F19" s="13" t="n">
         <x:v>13080761856.38868</x:v>
       </x:c>
-      <x:c r="G19" s="34" t="n">
+      <x:c r="G19" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="13" t="n">
+        <x:v>15656523133.862455</x:v>
+      </x:c>
+      <x:c r="I19" s="13" t="n">
+        <x:v>18605572385.110096</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1465,7 +1980,16 @@
       <x:c r="F20" s="13" t="n">
         <x:v>9159300914.392431</x:v>
       </x:c>
-      <x:c r="G20" s="34" t="n">
+      <x:c r="G20" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H20" s="13" t="n">
+        <x:v>12167852104.10709</x:v>
+      </x:c>
+      <x:c r="I20" s="13" t="n">
+        <x:v>15607989848.146132</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1488,7 +2012,16 @@
       <x:c r="F21" s="13" t="n">
         <x:v>3130748521.031528</x:v>
       </x:c>
-      <x:c r="G21" s="34" t="n">
+      <x:c r="G21" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H21" s="13" t="n">
+        <x:v>6566680026.082891</x:v>
+      </x:c>
+      <x:c r="I21" s="13" t="n">
+        <x:v>10500840470.741013</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1511,7 +2044,16 @@
       <x:c r="F22" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="34" t="n">
+      <x:c r="G22" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H22" s="13" t="n">
+        <x:v>3218317866.4553847</x:v>
+      </x:c>
+      <x:c r="I22" s="13" t="n">
+        <x:v>7641252295.103267</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1534,7 +2076,16 @@
       <x:c r="F23" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="34" t="n">
+      <x:c r="G23" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H23" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I23" s="13" t="n">
+        <x:v>4642180016.194417</x:v>
+      </x:c>
+      <x:c r="J23" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1557,8 +2108,17 @@
       <x:c r="F24" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="34" t="n">
+      <x:c r="G24" s="15" t="n">
         <x:v>0.0238</x:v>
+      </x:c>
+      <x:c r="H24" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I24" s="13" t="n">
+        <x:v>1783172385.53767</x:v>
+      </x:c>
+      <x:c r="J24" s="16" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="40" customHeight="1">
@@ -1580,8 +2140,17 @@
       <x:c r="F25" s="13" t="n">
         <x:v>-6628558782.736282</x:v>
       </x:c>
-      <x:c r="G25" s="34" t="n">
+      <x:c r="G25" s="15" t="n">
         <x:v>0.6261</x:v>
+      </x:c>
+      <x:c r="H25" s="13" t="n">
+        <x:v>-1474076193.2606115</x:v>
+      </x:c>
+      <x:c r="I25" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J25" s="16" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="32" customHeight="1">
@@ -1603,7 +2172,16 @@
       <x:c r="F26" s="13" t="n">
         <x:v>33778117570.529064</x:v>
       </x:c>
-      <x:c r="G26" s="34" t="n">
+      <x:c r="G26" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="13" t="n">
+        <x:v>34210057601.08914</x:v>
+      </x:c>
+      <x:c r="I26" s="13" t="n">
+        <x:v>34698530611.423164</x:v>
+      </x:c>
+      <x:c r="J26" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1626,7 +2204,16 @@
       <x:c r="F27" s="13" t="n">
         <x:v>31668108597.681282</x:v>
       </x:c>
-      <x:c r="G27" s="34" t="n">
+      <x:c r="G27" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H27" s="13" t="n">
+        <x:v>32527114729.79516</x:v>
+      </x:c>
+      <x:c r="I27" s="13" t="n">
+        <x:v>33509559043.162727</x:v>
+      </x:c>
+      <x:c r="J27" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1649,7 +2236,16 @@
       <x:c r="F28" s="13" t="n">
         <x:v>29556661043.891598</x:v>
       </x:c>
-      <x:c r="G28" s="34" t="n">
+      <x:c r="G28" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H28" s="13" t="n">
+        <x:v>30842849256.2782</x:v>
+      </x:c>
+      <x:c r="I28" s="13" t="n">
+        <x:v>32320901450.597527</x:v>
+      </x:c>
+      <x:c r="J28" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1672,7 +2268,16 @@
       <x:c r="F29" s="13" t="n">
         <x:v>27304006282.204006</x:v>
       </x:c>
-      <x:c r="G29" s="34" t="n">
+      <x:c r="G29" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" s="13" t="n">
+        <x:v>29019569080.341858</x:v>
+      </x:c>
+      <x:c r="I29" s="13" t="n">
+        <x:v>30986778491.79443</x:v>
+      </x:c>
+      <x:c r="J29" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1695,7 +2300,16 @@
       <x:c r="F30" s="13" t="n">
         <x:v>25189768965.019062</x:v>
       </x:c>
-      <x:c r="G30" s="34" t="n">
+      <x:c r="G30" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H30" s="13" t="n">
+        <x:v>27336694680.15538</x:v>
+      </x:c>
+      <x:c r="I30" s="13" t="n">
+        <x:v>29794893397.35088</x:v>
+      </x:c>
+      <x:c r="J30" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1718,7 +2332,16 @@
       <x:c r="F31" s="13" t="n">
         <x:v>23079261856.38868</x:v>
       </x:c>
-      <x:c r="G31" s="34" t="n">
+      <x:c r="G31" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H31" s="13" t="n">
+        <x:v>25655023133.862457</x:v>
+      </x:c>
+      <x:c r="I31" s="13" t="n">
+        <x:v>28604072385.110096</x:v>
+      </x:c>
+      <x:c r="J31" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1741,7 +2364,16 @@
       <x:c r="F32" s="13" t="n">
         <x:v>20824217581.0591</x:v>
       </x:c>
-      <x:c r="G32" s="34" t="n">
+      <x:c r="G32" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H32" s="13" t="n">
+        <x:v>23832768770.773758</x:v>
+      </x:c>
+      <x:c r="I32" s="13" t="n">
+        <x:v>27272906514.812794</x:v>
+      </x:c>
+      <x:c r="J32" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1764,7 +2396,16 @@
       <x:c r="F33" s="13" t="n">
         <x:v>16462081854.36486</x:v>
       </x:c>
-      <x:c r="G33" s="34" t="n">
+      <x:c r="G33" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H33" s="13" t="n">
+        <x:v>19898013359.416225</x:v>
+      </x:c>
+      <x:c r="I33" s="13" t="n">
+        <x:v>23832173804.07434</x:v>
+      </x:c>
+      <x:c r="J33" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1787,7 +2428,16 @@
       <x:c r="F34" s="13" t="n">
         <x:v>14348967128.466978</x:v>
       </x:c>
-      <x:c r="G34" s="34" t="n">
+      <x:c r="G34" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H34" s="13" t="n">
+        <x:v>18216067866.455383</x:v>
+      </x:c>
+      <x:c r="I34" s="13" t="n">
+        <x:v>22639002295.103268</x:v>
+      </x:c>
+      <x:c r="J34" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1810,7 +2460,16 @@
       <x:c r="F35" s="13" t="n">
         <x:v>12096380050.75672</x:v>
       </x:c>
-      <x:c r="G35" s="34" t="n">
+      <x:c r="G35" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H35" s="13" t="n">
+        <x:v>16393389465.185658</x:v>
+      </x:c>
+      <x:c r="I35" s="13" t="n">
+        <x:v>21306346682.861084</x:v>
+      </x:c>
+      <x:c r="J35" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1833,7 +2492,16 @@
       <x:c r="F36" s="13" t="n">
         <x:v>9984272764.528683</x:v>
       </x:c>
-      <x:c r="G36" s="34" t="n">
+      <x:c r="G36" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H36" s="13" t="n">
+        <x:v>14709568271.402107</x:v>
+      </x:c>
+      <x:c r="I36" s="13" t="n">
+        <x:v>20113755718.871002</x:v>
+      </x:c>
+      <x:c r="J36" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1856,8 +2524,17 @@
       <x:c r="F37" s="13" t="n">
         <x:v>3368441217.263717</x:v>
       </x:c>
-      <x:c r="G37" s="34" t="n">
+      <x:c r="G37" s="15" t="n">
         <x:v>0.0023</x:v>
+      </x:c>
+      <x:c r="H37" s="13" t="n">
+        <x:v>8522923806.739389</x:v>
+      </x:c>
+      <x:c r="I37" s="13" t="n">
+        <x:v>14417164754.880917</x:v>
+      </x:c>
+      <x:c r="J37" s="16" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="40" customHeight="1">
@@ -1879,7 +2556,16 @@
       <x:c r="F38" s="13" t="n">
         <x:v>33778117570.529064</x:v>
       </x:c>
-      <x:c r="G38" s="34" t="n">
+      <x:c r="G38" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H38" s="13" t="n">
+        <x:v>34210057601.08914</x:v>
+      </x:c>
+      <x:c r="I38" s="13" t="n">
+        <x:v>34698530611.423164</x:v>
+      </x:c>
+      <x:c r="J38" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1902,7 +2588,16 @@
       <x:c r="F39" s="13" t="n">
         <x:v>31668108597.681282</x:v>
       </x:c>
-      <x:c r="G39" s="34" t="n">
+      <x:c r="G39" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H39" s="13" t="n">
+        <x:v>32527114729.79516</x:v>
+      </x:c>
+      <x:c r="I39" s="13" t="n">
+        <x:v>33509559043.162727</x:v>
+      </x:c>
+      <x:c r="J39" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1925,7 +2620,16 @@
       <x:c r="F40" s="13" t="n">
         <x:v>29556661043.891598</x:v>
       </x:c>
-      <x:c r="G40" s="34" t="n">
+      <x:c r="G40" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H40" s="13" t="n">
+        <x:v>30842849256.2782</x:v>
+      </x:c>
+      <x:c r="I40" s="13" t="n">
+        <x:v>32320901450.597527</x:v>
+      </x:c>
+      <x:c r="J40" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1948,7 +2652,16 @@
       <x:c r="F41" s="13" t="n">
         <x:v>27304006282.204006</x:v>
       </x:c>
-      <x:c r="G41" s="34" t="n">
+      <x:c r="G41" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H41" s="13" t="n">
+        <x:v>29019569080.341858</x:v>
+      </x:c>
+      <x:c r="I41" s="13" t="n">
+        <x:v>30986778491.79443</x:v>
+      </x:c>
+      <x:c r="J41" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1971,7 +2684,16 @@
       <x:c r="F42" s="13" t="n">
         <x:v>25189768965.019062</x:v>
       </x:c>
-      <x:c r="G42" s="34" t="n">
+      <x:c r="G42" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H42" s="13" t="n">
+        <x:v>27336694680.15538</x:v>
+      </x:c>
+      <x:c r="I42" s="13" t="n">
+        <x:v>29794893397.35088</x:v>
+      </x:c>
+      <x:c r="J42" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1994,7 +2716,16 @@
       <x:c r="F43" s="13" t="n">
         <x:v>23079261856.38868</x:v>
       </x:c>
-      <x:c r="G43" s="34" t="n">
+      <x:c r="G43" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H43" s="13" t="n">
+        <x:v>25655023133.862457</x:v>
+      </x:c>
+      <x:c r="I43" s="13" t="n">
+        <x:v>28604072385.110096</x:v>
+      </x:c>
+      <x:c r="J43" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2017,7 +2748,16 @@
       <x:c r="F44" s="13" t="n">
         <x:v>20824217581.0591</x:v>
       </x:c>
-      <x:c r="G44" s="34" t="n">
+      <x:c r="G44" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H44" s="13" t="n">
+        <x:v>23832768770.773758</x:v>
+      </x:c>
+      <x:c r="I44" s="13" t="n">
+        <x:v>27272906514.812794</x:v>
+      </x:c>
+      <x:c r="J44" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2040,7 +2780,16 @@
       <x:c r="F45" s="13" t="n">
         <x:v>16462081854.36486</x:v>
       </x:c>
-      <x:c r="G45" s="34" t="n">
+      <x:c r="G45" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H45" s="13" t="n">
+        <x:v>19898013359.416225</x:v>
+      </x:c>
+      <x:c r="I45" s="13" t="n">
+        <x:v>23832173804.07434</x:v>
+      </x:c>
+      <x:c r="J45" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2063,7 +2812,16 @@
       <x:c r="F46" s="13" t="n">
         <x:v>14348967128.466978</x:v>
       </x:c>
-      <x:c r="G46" s="34" t="n">
+      <x:c r="G46" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H46" s="13" t="n">
+        <x:v>18216067866.455383</x:v>
+      </x:c>
+      <x:c r="I46" s="13" t="n">
+        <x:v>22639002295.103268</x:v>
+      </x:c>
+      <x:c r="J46" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2086,7 +2844,16 @@
       <x:c r="F47" s="13" t="n">
         <x:v>12096380050.75672</x:v>
       </x:c>
-      <x:c r="G47" s="34" t="n">
+      <x:c r="G47" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H47" s="13" t="n">
+        <x:v>16393389465.185658</x:v>
+      </x:c>
+      <x:c r="I47" s="13" t="n">
+        <x:v>21306346682.861084</x:v>
+      </x:c>
+      <x:c r="J47" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2109,7 +2876,16 @@
       <x:c r="F48" s="13" t="n">
         <x:v>9984272764.528683</x:v>
       </x:c>
-      <x:c r="G48" s="34" t="n">
+      <x:c r="G48" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H48" s="13" t="n">
+        <x:v>14709568271.402107</x:v>
+      </x:c>
+      <x:c r="I48" s="13" t="n">
+        <x:v>20113755718.871002</x:v>
+      </x:c>
+      <x:c r="J48" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2132,12 +2908,22 @@
       <x:c r="F49" s="18" t="n">
         <x:v>3368441217.263717</x:v>
       </x:c>
-      <x:c r="G49" s="35" t="n">
+      <x:c r="G49" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H49" s="18" t="n">
+        <x:v>8522923806.739389</x:v>
+      </x:c>
+      <x:c r="I49" s="18" t="n">
+        <x:v>14417164754.880917</x:v>
+      </x:c>
+      <x:c r="J49" s="21" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d670b316b6b48a8"/>
 </x:worksheet>
 </file>
 
@@ -2786,7 +3572,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="55" t="str">
-        <x:v>Horizon 2026-09-01 to 2027-08-31. Created 2026-10-17 12:53 ET. Seed 2026, 10,000 trials; rerunning with the same inputs and seed reproduces these results.</x:v>
+        <x:v>Horizon 2026-09-01 to 2027-08-31. Created 2026-10-17 13:07 ET. Seed 2026, 10,000 trials; rerunning with the same inputs and seed reproduces these results.</x:v>
       </x:c>
       <x:c r="B3" s="55"/>
       <x:c r="C3" s="55"/>
